--- a/php_api/database/touring.xlsx
+++ b/php_api/database/touring.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\projectgroup\php_api\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89A8591A-8624-4844-8AEF-05A778E97233}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B45FD2BB-B2A8-4D33-8681-E422E30247C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{125280A1-D0B5-483E-A083-4A2CE8C32E20}"/>
+    <workbookView xWindow="5520" yWindow="975" windowWidth="21600" windowHeight="11295" xr2:uid="{125280A1-D0B5-483E-A083-4A2CE8C32E20}"/>
   </bookViews>
   <sheets>
     <sheet name="DB touring" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="77">
   <si>
     <t>DATABASE touring</t>
   </si>
@@ -187,9 +187,6 @@
   </si>
   <si>
     <t>รูปภาพ</t>
-  </si>
-  <si>
-    <t>int(4) FK</t>
   </si>
   <si>
     <t>int(8) FK</t>
@@ -415,8 +412,8 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -424,8 +421,8 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -751,12 +748,12 @@
     <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="12" customFormat="1" ht="15">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:4" s="9" customFormat="1" ht="15">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:4" s="12" customFormat="1" ht="15"/>
+    <row r="2" spans="1:4" s="9" customFormat="1" ht="15"/>
     <row r="4" spans="1:4">
       <c r="B4" s="10" t="s">
         <v>11</v>
@@ -862,7 +859,7 @@
     </row>
     <row r="17" spans="2:4">
       <c r="B17" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>17</v>
@@ -878,7 +875,7 @@
     </row>
     <row r="19" spans="2:4">
       <c r="B19" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>21</v>
@@ -904,14 +901,14 @@
     </row>
     <row r="23" spans="2:4">
       <c r="B23" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C23" s="11"/>
       <c r="D23" s="11"/>
     </row>
     <row r="24" spans="2:4">
       <c r="B24" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>29</v>
@@ -975,7 +972,7 @@
     </row>
     <row r="32" spans="2:4">
       <c r="B32" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>17</v>
@@ -991,7 +988,7 @@
     </row>
     <row r="34" spans="2:4">
       <c r="B34" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>21</v>
@@ -1043,7 +1040,7 @@
         <v>20</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>45</v>
@@ -1055,13 +1052,13 @@
       <c r="D42" s="3"/>
     </row>
     <row r="43" spans="2:4">
-      <c r="B43" s="9"/>
-      <c r="C43" s="9"/>
+      <c r="B43" s="12"/>
+      <c r="C43" s="12"/>
       <c r="D43" s="2"/>
     </row>
     <row r="44" spans="2:4">
-      <c r="B44" s="9"/>
-      <c r="C44" s="9"/>
+      <c r="B44" s="12"/>
+      <c r="C44" s="12"/>
       <c r="D44" s="2"/>
     </row>
     <row r="45" spans="2:4">
@@ -1153,13 +1150,13 @@
     </row>
     <row r="56" spans="2:7">
       <c r="B56" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C56" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C56" s="3" t="s">
+      <c r="D56" s="3" t="s">
         <v>74</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="57" spans="2:7">
@@ -1185,25 +1182,25 @@
     </row>
     <row r="61" spans="2:7">
       <c r="G61" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="62" spans="2:7">
       <c r="B62" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C62" s="5"/>
       <c r="D62" s="6"/>
     </row>
     <row r="63" spans="2:7">
       <c r="B63" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C63" s="7" t="s">
         <v>31</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="64" spans="2:7">
@@ -1213,10 +1210,10 @@
     </row>
     <row r="65" spans="2:4">
       <c r="B65" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D65" s="8" t="s">
         <v>38</v>
@@ -1232,7 +1229,7 @@
         <v>23</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D67" s="8" t="s">
         <v>46</v>
@@ -1248,7 +1245,7 @@
         <v>1</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D69" s="8" t="s">
         <v>32</v>
@@ -1261,13 +1258,13 @@
     </row>
     <row r="71" spans="2:4">
       <c r="B71" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="72" spans="2:4">
@@ -1277,13 +1274,13 @@
     </row>
     <row r="73" spans="2:4">
       <c r="B73" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="74" spans="2:4">
@@ -1293,13 +1290,13 @@
     </row>
     <row r="75" spans="2:4">
       <c r="B75" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="76" spans="2:4">
@@ -1309,13 +1306,13 @@
     </row>
     <row r="77" spans="2:4">
       <c r="B77" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C77" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="78" spans="2:4">
@@ -1325,39 +1322,50 @@
     </row>
   </sheetData>
   <mergeCells count="101">
-    <mergeCell ref="B56:B57"/>
-    <mergeCell ref="C56:C57"/>
-    <mergeCell ref="D56:D57"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="D19:D20"/>
-    <mergeCell ref="B71:B72"/>
-    <mergeCell ref="C71:C72"/>
-    <mergeCell ref="D71:D72"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B63:B64"/>
-    <mergeCell ref="C63:C64"/>
-    <mergeCell ref="D63:D64"/>
-    <mergeCell ref="B65:B66"/>
-    <mergeCell ref="C65:C66"/>
-    <mergeCell ref="D65:D66"/>
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="C52:C53"/>
-    <mergeCell ref="B73:B74"/>
-    <mergeCell ref="C73:C74"/>
-    <mergeCell ref="D73:D74"/>
-    <mergeCell ref="B67:B68"/>
-    <mergeCell ref="C67:C68"/>
-    <mergeCell ref="D67:D68"/>
-    <mergeCell ref="B69:B70"/>
-    <mergeCell ref="C69:C70"/>
-    <mergeCell ref="D69:D70"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="B50:B51"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="B75:B76"/>
+    <mergeCell ref="C75:C76"/>
+    <mergeCell ref="D75:D76"/>
+    <mergeCell ref="B77:B78"/>
+    <mergeCell ref="C77:C78"/>
+    <mergeCell ref="D77:D78"/>
+    <mergeCell ref="D58:D59"/>
+    <mergeCell ref="B45:D45"/>
+    <mergeCell ref="D39:D40"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="D46:D47"/>
+    <mergeCell ref="D48:D49"/>
+    <mergeCell ref="D52:D53"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="C43:C44"/>
+    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="C46:C47"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="D54:D55"/>
+    <mergeCell ref="D50:D51"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="C32:C33"/>
     <mergeCell ref="A1:XFD2"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="C5:C6"/>
@@ -1382,50 +1390,39 @@
     <mergeCell ref="D11:D12"/>
     <mergeCell ref="D13:D14"/>
     <mergeCell ref="D15:D16"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="D54:D55"/>
-    <mergeCell ref="D50:D51"/>
-    <mergeCell ref="D58:D59"/>
-    <mergeCell ref="B45:D45"/>
-    <mergeCell ref="D39:D40"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="D46:D47"/>
-    <mergeCell ref="D48:D49"/>
-    <mergeCell ref="D52:D53"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="C43:C44"/>
-    <mergeCell ref="B46:B47"/>
-    <mergeCell ref="C46:C47"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="D32:D33"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="B75:B76"/>
-    <mergeCell ref="C75:C76"/>
-    <mergeCell ref="D75:D76"/>
-    <mergeCell ref="B77:B78"/>
-    <mergeCell ref="C77:C78"/>
-    <mergeCell ref="D77:D78"/>
+    <mergeCell ref="B73:B74"/>
+    <mergeCell ref="C73:C74"/>
+    <mergeCell ref="D73:D74"/>
+    <mergeCell ref="B67:B68"/>
+    <mergeCell ref="C67:C68"/>
+    <mergeCell ref="D67:D68"/>
+    <mergeCell ref="B69:B70"/>
+    <mergeCell ref="C69:C70"/>
+    <mergeCell ref="D69:D70"/>
+    <mergeCell ref="B56:B57"/>
+    <mergeCell ref="C56:C57"/>
+    <mergeCell ref="D56:D57"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="B71:B72"/>
+    <mergeCell ref="C71:C72"/>
+    <mergeCell ref="D71:D72"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B63:B64"/>
+    <mergeCell ref="C63:C64"/>
+    <mergeCell ref="D63:D64"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="C65:C66"/>
+    <mergeCell ref="D65:D66"/>
+    <mergeCell ref="C48:C49"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="C52:C53"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="B52:B53"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/php_api/database/touring.xlsx
+++ b/php_api/database/touring.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\projectgroup\php_api\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B45FD2BB-B2A8-4D33-8681-E422E30247C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D249C2A-9834-4330-9275-087172DD1F8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5520" yWindow="975" windowWidth="21600" windowHeight="11295" xr2:uid="{125280A1-D0B5-483E-A083-4A2CE8C32E20}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{125280A1-D0B5-483E-A083-4A2CE8C32E20}"/>
   </bookViews>
   <sheets>
     <sheet name="DB touring" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="82">
   <si>
     <t>DATABASE touring</t>
   </si>
@@ -69,9 +69,6 @@
     <t>timestamp</t>
   </si>
   <si>
-    <t>TABLE employee</t>
-  </si>
-  <si>
     <t>efull_name</t>
   </si>
   <si>
@@ -90,9 +87,6 @@
     <t>varchar(20)</t>
   </si>
   <si>
-    <t>TABLE categories</t>
-  </si>
-  <si>
     <t>category_id</t>
   </si>
   <si>
@@ -102,9 +96,6 @@
     <t>varchar(255)</t>
   </si>
   <si>
-    <t>TABLE attraction</t>
-  </si>
-  <si>
     <t>att_id</t>
   </si>
   <si>
@@ -195,9 +186,6 @@
     <t>cust_id</t>
   </si>
   <si>
-    <t>TABLE bookings</t>
-  </si>
-  <si>
     <t>booking_id</t>
   </si>
   <si>
@@ -264,7 +252,34 @@
     <t>วันที่ทำรายการ</t>
   </si>
   <si>
-    <t>TABLE customers</t>
+    <t>เก็บข้อมูลพนักงานในบริษัท</t>
+  </si>
+  <si>
+    <t>ตารางพนักงาน (Employee)</t>
+  </si>
+  <si>
+    <t>ตารางลูกค้า (customers)</t>
+  </si>
+  <si>
+    <t>ตารางหมวดหมู่สถานที่ท่องเที่ยว (categories)</t>
+  </si>
+  <si>
+    <t>ตารางสถานที่ท่องเที่ยว (attraction)</t>
+  </si>
+  <si>
+    <t>ตารางการจอง (bookings)</t>
+  </si>
+  <si>
+    <t>เก็บข้อมูลลูกค้าที่ทำการจองทัวร์</t>
+  </si>
+  <si>
+    <t>เก็บข้อมูลหมวดหมู่สถานที่ท่องเที่ยว</t>
+  </si>
+  <si>
+    <t>เก็บข้อมูลสถานที่ท่องเที่ยว</t>
+  </si>
+  <si>
+    <t>เก็บข้อมูลการจองทัวร์</t>
   </si>
 </sst>
 </file>
@@ -298,7 +313,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -313,18 +328,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="6" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -355,6 +364,44 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -365,20 +412,7 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
+      <top/>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -397,32 +431,32 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -738,7 +772,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D4EA20D-7F93-4EDA-AF26-F1891034FE50}">
-  <dimension ref="A1:G78"/>
+  <dimension ref="A1:G84"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -748,60 +782,54 @@
     <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="9" customFormat="1" ht="15">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:4" s="4" customFormat="1" ht="15">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:4" s="9" customFormat="1" ht="15"/>
+    <row r="2" spans="1:4" s="4" customFormat="1" ht="15"/>
     <row r="4" spans="1:4">
-      <c r="B4" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
+      <c r="B4" s="1" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C5" s="6"/>
+      <c r="D5" s="7"/>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="B6" s="8"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="10"/>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="B7" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C7" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="B7" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>33</v>
-      </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
     </row>
     <row r="9" spans="1:4">
       <c r="B9" s="3" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -811,13 +839,13 @@
     </row>
     <row r="11" spans="1:4">
       <c r="B11" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -827,13 +855,13 @@
     </row>
     <row r="13" spans="1:4">
       <c r="B13" s="3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -843,13 +871,13 @@
     </row>
     <row r="15" spans="1:4">
       <c r="B15" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -859,13 +887,13 @@
     </row>
     <row r="17" spans="2:4">
       <c r="B17" s="3" t="s">
-        <v>67</v>
+        <v>9</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -875,13 +903,13 @@
     </row>
     <row r="19" spans="2:4">
       <c r="B19" s="3" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20" spans="2:4">
@@ -890,539 +918,582 @@
       <c r="D20" s="3"/>
     </row>
     <row r="21" spans="2:4">
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
+      <c r="B21" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="22" spans="2:4">
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
     </row>
     <row r="23" spans="2:4">
-      <c r="B23" s="11" t="s">
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+    </row>
+    <row r="24" spans="2:4">
+      <c r="B24" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+    </row>
+    <row r="25" spans="2:4">
+      <c r="B25" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C25" s="6"/>
+      <c r="D25" s="7"/>
+    </row>
+    <row r="26" spans="2:4">
+      <c r="B26" s="8"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="10"/>
+    </row>
+    <row r="27" spans="2:4">
+      <c r="B27" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4">
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
+    </row>
+    <row r="29" spans="2:4">
+      <c r="B29" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="30" spans="2:4">
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+    </row>
+    <row r="31" spans="2:4">
+      <c r="B31" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4">
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+    </row>
+    <row r="33" spans="2:4">
+      <c r="B33" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4">
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+    </row>
+    <row r="35" spans="2:4">
+      <c r="B35" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4">
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
+    </row>
+    <row r="37" spans="2:4">
+      <c r="B37" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4">
+      <c r="B38" s="3"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="3"/>
+    </row>
+    <row r="39" spans="2:4">
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+    </row>
+    <row r="40" spans="2:4">
+      <c r="B40" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+    </row>
+    <row r="41" spans="2:4">
+      <c r="B41" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C41" s="6"/>
+      <c r="D41" s="7"/>
+    </row>
+    <row r="42" spans="2:4">
+      <c r="B42" s="8"/>
+      <c r="C42" s="9"/>
+      <c r="D42" s="10"/>
+    </row>
+    <row r="43" spans="2:4">
+      <c r="B43" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C43" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D43" s="11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="44" spans="2:4">
+      <c r="B44" s="11"/>
+      <c r="C44" s="11"/>
+      <c r="D44" s="11"/>
+    </row>
+    <row r="45" spans="2:4">
+      <c r="B45" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="46" spans="2:4">
+      <c r="B46" s="3"/>
+      <c r="C46" s="3"/>
+      <c r="D46" s="3"/>
+    </row>
+    <row r="47" spans="2:4">
+      <c r="B47" s="12"/>
+      <c r="C47" s="12"/>
+      <c r="D47" s="2"/>
+    </row>
+    <row r="48" spans="2:4">
+      <c r="B48" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="C48" s="12"/>
+      <c r="D48" s="2"/>
+    </row>
+    <row r="49" spans="2:4">
+      <c r="B49" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
-    </row>
-    <row r="24" spans="2:4">
-      <c r="B24" s="7" t="s">
+      <c r="C49" s="6"/>
+      <c r="D49" s="7"/>
+    </row>
+    <row r="50" spans="2:4">
+      <c r="B50" s="8"/>
+      <c r="C50" s="9"/>
+      <c r="D50" s="10"/>
+    </row>
+    <row r="51" spans="2:4">
+      <c r="B51" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C51" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="D51" s="11" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="52" spans="2:4">
+      <c r="B52" s="11"/>
+      <c r="C52" s="11"/>
+      <c r="D52" s="11"/>
+    </row>
+    <row r="53" spans="2:4">
+      <c r="B53" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="54" spans="2:4">
+      <c r="B54" s="3"/>
+      <c r="C54" s="3"/>
+      <c r="D54" s="3"/>
+    </row>
+    <row r="55" spans="2:4">
+      <c r="B55" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C55" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="D55" s="11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="56" spans="2:4">
+      <c r="B56" s="11"/>
+      <c r="C56" s="11"/>
+      <c r="D56" s="11"/>
+    </row>
+    <row r="57" spans="2:4">
+      <c r="B57" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="58" spans="2:4">
+      <c r="B58" s="3"/>
+      <c r="C58" s="3"/>
+      <c r="D58" s="3"/>
+    </row>
+    <row r="59" spans="2:4">
+      <c r="B59" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="60" spans="2:4">
+      <c r="B60" s="3"/>
+      <c r="C60" s="3"/>
+      <c r="D60" s="3"/>
+    </row>
+    <row r="61" spans="2:4">
+      <c r="B61" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="62" spans="2:4">
+      <c r="B62" s="3"/>
+      <c r="C62" s="3"/>
+      <c r="D62" s="3"/>
+    </row>
+    <row r="63" spans="2:4">
+      <c r="B63" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="64" spans="2:4">
+      <c r="B64" s="3"/>
+      <c r="C64" s="3"/>
+      <c r="D64" s="3"/>
+    </row>
+    <row r="66" spans="2:7">
+      <c r="B66" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="67" spans="2:7">
+      <c r="B67" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C67" s="6"/>
+      <c r="D67" s="7"/>
+    </row>
+    <row r="68" spans="2:7">
+      <c r="B68" s="8"/>
+      <c r="C68" s="9"/>
+      <c r="D68" s="10"/>
+    </row>
+    <row r="69" spans="2:7">
+      <c r="B69" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="C69" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="D69" s="11" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="70" spans="2:7">
+      <c r="B70" s="11"/>
+      <c r="C70" s="11"/>
+      <c r="D70" s="11"/>
+    </row>
+    <row r="71" spans="2:7">
+      <c r="B71" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="C71" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="D71" s="11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="72" spans="2:7">
+      <c r="B72" s="11"/>
+      <c r="C72" s="11"/>
+      <c r="D72" s="11"/>
+    </row>
+    <row r="73" spans="2:7">
+      <c r="B73" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C73" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="D73" s="11" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="74" spans="2:7">
+      <c r="B74" s="11"/>
+      <c r="C74" s="11"/>
+      <c r="D74" s="11"/>
+    </row>
+    <row r="75" spans="2:7">
+      <c r="B75" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C75" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="D75" s="11" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="76" spans="2:7">
+      <c r="B76" s="11"/>
+      <c r="C76" s="11"/>
+      <c r="D76" s="11"/>
+    </row>
+    <row r="77" spans="2:7">
+      <c r="B77" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C24" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="25" spans="2:4">
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-    </row>
-    <row r="26" spans="2:4">
-      <c r="B26" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="27" spans="2:4">
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-    </row>
-    <row r="28" spans="2:4">
-      <c r="B28" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="29" spans="2:4">
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
-    </row>
-    <row r="30" spans="2:4">
-      <c r="B30" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="31" spans="2:4">
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
-    </row>
-    <row r="32" spans="2:4">
-      <c r="B32" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="33" spans="2:4">
-      <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
-      <c r="D33" s="3"/>
-    </row>
-    <row r="34" spans="2:4">
-      <c r="B34" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="35" spans="2:4">
-      <c r="B35" s="3"/>
-      <c r="C35" s="3"/>
-      <c r="D35" s="3"/>
-    </row>
-    <row r="36" spans="2:4">
-      <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
-    </row>
-    <row r="37" spans="2:4">
-      <c r="B37" s="2"/>
-      <c r="C37" s="2"/>
-      <c r="D37" s="2"/>
-    </row>
-    <row r="38" spans="2:4">
-      <c r="B38" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C38" s="5"/>
-      <c r="D38" s="6"/>
-    </row>
-    <row r="39" spans="2:4">
-      <c r="B39" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C39" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D39" s="7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="40" spans="2:4">
-      <c r="B40" s="7"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="7"/>
-    </row>
-    <row r="41" spans="2:4">
-      <c r="B41" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C41" s="3" t="s">
+      <c r="C77" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D77" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="D41" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="42" spans="2:4">
-      <c r="B42" s="3"/>
-      <c r="C42" s="3"/>
-      <c r="D42" s="3"/>
-    </row>
-    <row r="43" spans="2:4">
-      <c r="B43" s="12"/>
-      <c r="C43" s="12"/>
-      <c r="D43" s="2"/>
-    </row>
-    <row r="44" spans="2:4">
-      <c r="B44" s="12"/>
-      <c r="C44" s="12"/>
-      <c r="D44" s="2"/>
-    </row>
-    <row r="45" spans="2:4">
-      <c r="B45" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C45" s="5"/>
-      <c r="D45" s="6"/>
-    </row>
-    <row r="46" spans="2:4">
-      <c r="B46" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C46" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="D46" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="47" spans="2:4">
-      <c r="B47" s="7"/>
-      <c r="C47" s="7"/>
-      <c r="D47" s="7"/>
-    </row>
-    <row r="48" spans="2:4">
-      <c r="B48" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="49" spans="2:7">
-      <c r="B49" s="3"/>
-      <c r="C49" s="3"/>
-      <c r="D49" s="3"/>
-    </row>
-    <row r="50" spans="2:7">
-      <c r="B50" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C50" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D50" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="51" spans="2:7">
-      <c r="B51" s="8"/>
-      <c r="C51" s="8"/>
-      <c r="D51" s="8"/>
-    </row>
-    <row r="52" spans="2:7">
-      <c r="B52" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="53" spans="2:7">
-      <c r="B53" s="3"/>
-      <c r="C53" s="3"/>
-      <c r="D53" s="3"/>
-    </row>
-    <row r="54" spans="2:7">
-      <c r="B54" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="55" spans="2:7">
-      <c r="B55" s="3"/>
-      <c r="C55" s="3"/>
-      <c r="D55" s="3"/>
-    </row>
-    <row r="56" spans="2:7">
-      <c r="B56" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="57" spans="2:7">
-      <c r="B57" s="3"/>
-      <c r="C57" s="3"/>
-      <c r="D57" s="3"/>
-    </row>
-    <row r="58" spans="2:7">
-      <c r="B58" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="59" spans="2:7">
-      <c r="B59" s="3"/>
-      <c r="C59" s="3"/>
-      <c r="D59" s="3"/>
-    </row>
-    <row r="61" spans="2:7">
-      <c r="G61" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="62" spans="2:7">
-      <c r="B62" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C62" s="5"/>
-      <c r="D62" s="6"/>
-    </row>
-    <row r="63" spans="2:7">
-      <c r="B63" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="C63" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="D63" s="7" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="64" spans="2:7">
-      <c r="B64" s="7"/>
-      <c r="C64" s="7"/>
-      <c r="D64" s="7"/>
-    </row>
-    <row r="65" spans="2:4">
-      <c r="B65" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="C65" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D65" s="8" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="66" spans="2:4">
-      <c r="B66" s="8"/>
-      <c r="C66" s="8"/>
-      <c r="D66" s="8"/>
-    </row>
-    <row r="67" spans="2:4">
-      <c r="B67" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C67" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="D67" s="8" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="68" spans="2:4">
-      <c r="B68" s="8"/>
-      <c r="C68" s="8"/>
-      <c r="D68" s="8"/>
-    </row>
-    <row r="69" spans="2:4">
-      <c r="B69" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C69" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D69" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="70" spans="2:4">
-      <c r="B70" s="8"/>
-      <c r="C70" s="8"/>
-      <c r="D70" s="8"/>
-    </row>
-    <row r="71" spans="2:4">
-      <c r="B71" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D71" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="72" spans="2:4">
-      <c r="B72" s="3"/>
-      <c r="C72" s="3"/>
-      <c r="D72" s="3"/>
-    </row>
-    <row r="73" spans="2:4">
-      <c r="B73" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D73" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="74" spans="2:4">
-      <c r="B74" s="3"/>
-      <c r="C74" s="3"/>
-      <c r="D74" s="3"/>
-    </row>
-    <row r="75" spans="2:4">
-      <c r="B75" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D75" s="3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="76" spans="2:4">
-      <c r="B76" s="3"/>
-      <c r="C76" s="3"/>
-      <c r="D76" s="3"/>
-    </row>
-    <row r="77" spans="2:4">
-      <c r="B77" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D77" s="3" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="78" spans="2:4">
+    </row>
+    <row r="78" spans="2:7">
       <c r="B78" s="3"/>
       <c r="C78" s="3"/>
       <c r="D78" s="3"/>
     </row>
+    <row r="79" spans="2:7">
+      <c r="B79" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="80" spans="2:7">
+      <c r="B80" s="3"/>
+      <c r="C80" s="3"/>
+      <c r="D80" s="3"/>
+    </row>
+    <row r="81" spans="2:4">
+      <c r="B81" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="82" spans="2:4">
+      <c r="B82" s="3"/>
+      <c r="C82" s="3"/>
+      <c r="D82" s="3"/>
+    </row>
+    <row r="83" spans="2:4">
+      <c r="B83" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="84" spans="2:4">
+      <c r="B84" s="3"/>
+      <c r="C84" s="3"/>
+      <c r="D84" s="3"/>
+    </row>
   </sheetData>
-  <mergeCells count="101">
+  <mergeCells count="99">
+    <mergeCell ref="B5:D6"/>
+    <mergeCell ref="B67:D68"/>
+    <mergeCell ref="B49:D50"/>
+    <mergeCell ref="B41:D42"/>
+    <mergeCell ref="B25:D26"/>
+    <mergeCell ref="B77:B78"/>
+    <mergeCell ref="C77:C78"/>
+    <mergeCell ref="D77:D78"/>
+    <mergeCell ref="B69:B70"/>
+    <mergeCell ref="C69:C70"/>
+    <mergeCell ref="D69:D70"/>
+    <mergeCell ref="B71:B72"/>
+    <mergeCell ref="C71:C72"/>
+    <mergeCell ref="D71:D72"/>
+    <mergeCell ref="C73:C74"/>
+    <mergeCell ref="D73:D74"/>
     <mergeCell ref="B75:B76"/>
     <mergeCell ref="C75:C76"/>
     <mergeCell ref="D75:D76"/>
-    <mergeCell ref="B77:B78"/>
-    <mergeCell ref="C77:C78"/>
-    <mergeCell ref="D77:D78"/>
-    <mergeCell ref="D58:D59"/>
-    <mergeCell ref="B45:D45"/>
-    <mergeCell ref="D39:D40"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="D46:D47"/>
-    <mergeCell ref="D48:D49"/>
-    <mergeCell ref="D52:D53"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="B61:B62"/>
+    <mergeCell ref="C61:C62"/>
+    <mergeCell ref="D61:D62"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="C53:C54"/>
+    <mergeCell ref="B63:B64"/>
+    <mergeCell ref="C63:C64"/>
+    <mergeCell ref="C57:C58"/>
+    <mergeCell ref="B59:B60"/>
+    <mergeCell ref="C59:C60"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="C55:C56"/>
+    <mergeCell ref="B57:B58"/>
+    <mergeCell ref="A1:XFD2"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:C8"/>
     <mergeCell ref="B43:B44"/>
     <mergeCell ref="C43:C44"/>
-    <mergeCell ref="B46:B47"/>
-    <mergeCell ref="C46:C47"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="D54:D55"/>
-    <mergeCell ref="D50:D51"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="D32:D33"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="A1:XFD2"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:C8"/>
     <mergeCell ref="B9:B10"/>
     <mergeCell ref="C9:C10"/>
     <mergeCell ref="B11:B12"/>
     <mergeCell ref="C11:C12"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="C31:C32"/>
     <mergeCell ref="D7:D8"/>
     <mergeCell ref="D9:D10"/>
     <mergeCell ref="D11:D12"/>
     <mergeCell ref="D13:D14"/>
     <mergeCell ref="D15:D16"/>
-    <mergeCell ref="B73:B74"/>
-    <mergeCell ref="C73:C74"/>
-    <mergeCell ref="D73:D74"/>
-    <mergeCell ref="B67:B68"/>
-    <mergeCell ref="C67:C68"/>
-    <mergeCell ref="D67:D68"/>
-    <mergeCell ref="B69:B70"/>
-    <mergeCell ref="C69:C70"/>
-    <mergeCell ref="D69:D70"/>
-    <mergeCell ref="B56:B57"/>
-    <mergeCell ref="C56:C57"/>
-    <mergeCell ref="D56:D57"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="B19:B20"/>
     <mergeCell ref="C19:C20"/>
     <mergeCell ref="D19:D20"/>
-    <mergeCell ref="B71:B72"/>
-    <mergeCell ref="C71:C72"/>
-    <mergeCell ref="D71:D72"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B63:B64"/>
-    <mergeCell ref="C63:C64"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="D59:D60"/>
+    <mergeCell ref="D55:D56"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="D35:D36"/>
+    <mergeCell ref="D37:D38"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="B37:B38"/>
+    <mergeCell ref="C37:C38"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="B81:B82"/>
+    <mergeCell ref="C81:C82"/>
+    <mergeCell ref="D81:D82"/>
+    <mergeCell ref="B83:B84"/>
+    <mergeCell ref="C83:C84"/>
+    <mergeCell ref="D83:D84"/>
     <mergeCell ref="D63:D64"/>
-    <mergeCell ref="B65:B66"/>
-    <mergeCell ref="C65:C66"/>
-    <mergeCell ref="D65:D66"/>
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="C52:C53"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="B50:B51"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="D43:D44"/>
+    <mergeCell ref="D45:D46"/>
+    <mergeCell ref="D51:D52"/>
+    <mergeCell ref="D53:D54"/>
+    <mergeCell ref="D57:D58"/>
+    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="C45:C46"/>
+    <mergeCell ref="B51:B52"/>
+    <mergeCell ref="C51:C52"/>
+    <mergeCell ref="B53:B54"/>
+    <mergeCell ref="B79:B80"/>
+    <mergeCell ref="C79:C80"/>
+    <mergeCell ref="D79:D80"/>
+    <mergeCell ref="B73:B74"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
